--- a/middle-to-gun/Excel/Ear_耳朵.xlsx
+++ b/middle-to-gun/Excel/Ear_耳朵.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" tabRatio="500"/>
+    <workbookView windowWidth="24750" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="132">
   <si>
     <t>Int</t>
   </si>
@@ -64,6 +64,9 @@
     <t>0|0|0|0|0|0|1|1|1</t>
   </si>
   <si>
+    <t>0|0|20|0|0|0|1|1|1</t>
+  </si>
+  <si>
     <t>围巾</t>
   </si>
   <si>
@@ -136,9 +139,6 @@
     <t>蝙蝠</t>
   </si>
   <si>
-    <t>0|0|20|0|0|0|1|1|1</t>
-  </si>
-  <si>
     <t>花瓣环绕</t>
   </si>
   <si>
@@ -242,6 +242,189 @@
   </si>
   <si>
     <t>恭喜发财</t>
+  </si>
+  <si>
+    <t>南瓜</t>
+  </si>
+  <si>
+    <t>0|0|-5|0|0|0|0.6|0.6|0.6</t>
+  </si>
+  <si>
+    <t>头套</t>
+  </si>
+  <si>
+    <t>0|0|-5|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|10|0|0|0|0.8|0.8|0.8</t>
+  </si>
+  <si>
+    <t>0|0|15|0|0|0|0.8|0.8|0.8</t>
+  </si>
+  <si>
+    <t>0|-1.3|-5|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|4|12|-5|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-3|10|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|10|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|8|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|7|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2|10|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|11|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-1|-2|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-3|4|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-1|16|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-3|12|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-1|12|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-1|15|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>2|-4|12|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2.5|13|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2|12|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|2|13|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-3|11|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2.5|12|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2.5|10|0|0|0|0.3|0.3|0.3</t>
+  </si>
+  <si>
+    <t>0|-3|8|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2.5|8|0|0|0|1.2|1.2|1.2</t>
+  </si>
+  <si>
+    <t>0|-1|3|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-5|5|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2.5|5|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|5|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2.5|14|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>-3|-5|-5|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-4|-7|0|0|0|1.2|1.2|1.2</t>
+  </si>
+  <si>
+    <t>0|-2|0|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>3|0|18|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|-9|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-4|10|0|0|0|0.8|0.8|0.8</t>
+  </si>
+  <si>
+    <t>0|-4|6|0|0|0|0.8|0.8|0.8</t>
+  </si>
+  <si>
+    <t>0|-2.5|5|0|0|0|0.8|0.8|0.8</t>
+  </si>
+  <si>
+    <t>0|-3|6|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-3|-2|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-1.5|-3|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2.5|-3|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2|3|0|0|0|0.8|0.8|0.8</t>
+  </si>
+  <si>
+    <t>0|-2.5|2.5|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-6|-6|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-1.33|12|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2.5|12|0|0|0|0.8|0.8|0.8</t>
+  </si>
+  <si>
+    <t>0|0|22|0|0|0|0.8|0.8|0.8</t>
+  </si>
+  <si>
+    <t>0|-4.5|15|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-5|16|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-4|10|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|2|12|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2|2|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|17|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|0|-11|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-3|9|0|0|0|1|1|1</t>
+  </si>
+  <si>
+    <t>0|-2|11|0|0|0|1|1|1</t>
   </si>
 </sst>
 </file>
@@ -890,7 +1073,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -917,6 +1100,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1455,6 +1644,7 @@
   <dimension ref="A1:U219"/>
   <sheetFormatPr defaultColWidth="12.025" defaultRowHeight="16.5"/>
   <cols>
+    <col min="3" max="3" width="35.125" customWidth="1"/>
     <col min="4" max="4" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1609,14 +1799,12 @@
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="1">
+        <v>677382</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" s="1">
-        <v>295506</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -1646,7 +1834,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="1">
-        <v>352615</v>
+        <v>295506</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>10</v>
@@ -1679,9 +1867,9 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>404433</v>
-      </c>
-      <c r="D8" s="1" t="s">
+        <v>352615</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="1">
@@ -1712,9 +1900,9 @@
         <v>14</v>
       </c>
       <c r="C9" s="1">
-        <v>404473</v>
-      </c>
-      <c r="D9" s="4" t="s">
+        <v>404433</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1">
@@ -1745,7 +1933,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="1">
-        <v>441348</v>
+        <v>404473</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>10</v>
@@ -1770,18 +1958,18 @@
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
     </row>
-    <row r="11" ht="17.25" spans="1:21">
+    <row r="11" spans="1:21">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="5">
-        <v>142935</v>
+      <c r="C11" s="1">
+        <v>441348</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1803,18 +1991,18 @@
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" ht="17.25" spans="1:21">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5">
+        <v>142935</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="C12" s="1">
-        <v>462790</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -1841,13 +2029,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>462790</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C13" s="1">
-        <v>462791</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1877,10 +2065,10 @@
         <v>21</v>
       </c>
       <c r="C14" s="1">
-        <v>441349</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>10</v>
+        <v>462791</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -1907,13 +2095,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
-        <v>13728</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>22</v>
+        <v>441349</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
@@ -1939,16 +2127,16 @@
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1">
+        <v>13728</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="7">
-        <v>169404</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="7">
+      <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1"/>
@@ -1972,13 +2160,13 @@
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1">
-        <v>200911</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="B17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="7">
+        <v>169404</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="7">
@@ -2006,13 +2194,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="1">
+        <v>200911</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C18" s="1">
-        <v>88831</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E18" s="7">
         <v>0</v>
@@ -2039,13 +2227,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1">
-        <v>88818</v>
+        <v>88831</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E19" s="7">
         <v>0</v>
@@ -2072,12 +2260,12 @@
         <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1">
-        <v>88825</v>
-      </c>
-      <c r="D20" s="9" t="s">
+        <v>88818</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="7">
@@ -2105,13 +2293,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1">
+        <v>88825</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="C21" s="1">
-        <v>287819</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="E21" s="7">
         <v>0</v>
@@ -2138,13 +2326,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="1">
+        <v>287819</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C22" s="1">
-        <v>26155</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="7">
         <v>0</v>
@@ -2171,15 +2359,15 @@
         <v>19</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1">
+        <v>26155</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="1">
-        <v>451246</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="E23" s="7">
         <v>0</v>
       </c>
       <c r="F23" s="1"/>
@@ -2207,10 +2395,10 @@
         <v>34</v>
       </c>
       <c r="C24" s="1">
-        <v>452716</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>35</v>
+        <v>451246</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
@@ -2237,13 +2425,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="1">
-        <v>340179</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>10</v>
+        <v>452716</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -2270,10 +2458,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1">
-        <v>295800</v>
+        <v>340179</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>10</v>
@@ -2302,11 +2490,9 @@
       <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="B27" s="3"/>
       <c r="C27" s="1">
-        <v>235888</v>
+        <v>340181</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>10</v>
@@ -2336,10 +2522,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="1">
-        <v>295801</v>
+        <v>295800</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>10</v>
@@ -2369,13 +2555,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
-        <v>26158</v>
+        <v>235888</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -2402,15 +2588,15 @@
         <v>26</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1">
-        <v>184435</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="7">
+        <v>295801</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="1"/>
@@ -2435,13 +2621,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C31" s="1">
-        <v>452232</v>
+        <v>26158</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
@@ -2468,13 +2654,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C32" s="1">
-        <v>452233</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>10</v>
+        <v>184435</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
@@ -2504,9 +2690,9 @@
         <v>43</v>
       </c>
       <c r="C33" s="1">
-        <v>452234</v>
-      </c>
-      <c r="D33" s="1" t="s">
+        <v>452232</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="1">
@@ -2537,7 +2723,7 @@
         <v>43</v>
       </c>
       <c r="C34" s="1">
-        <v>452235</v>
+        <v>452233</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>10</v>
@@ -2567,12 +2753,12 @@
         <v>31</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="1">
-        <v>471540</v>
-      </c>
-      <c r="D35" s="4" t="s">
+        <v>452234</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="1">
@@ -2600,12 +2786,12 @@
         <v>32</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" s="1">
-        <v>471541</v>
-      </c>
-      <c r="D36" s="1" t="s">
+        <v>452235</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="1">
@@ -2636,7 +2822,7 @@
         <v>44</v>
       </c>
       <c r="C37" s="1">
-        <v>471542</v>
+        <v>471540</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>10</v>
@@ -2669,9 +2855,9 @@
         <v>44</v>
       </c>
       <c r="C38" s="1">
-        <v>471543</v>
-      </c>
-      <c r="D38" s="4" t="s">
+        <v>471541</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="1">
@@ -2699,12 +2885,12 @@
         <v>35</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="1">
-        <v>502350</v>
-      </c>
-      <c r="D39" s="1" t="s">
+        <v>471542</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="1">
@@ -2732,10 +2918,10 @@
         <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C40" s="1">
-        <v>502351</v>
+        <v>471543</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>10</v>
@@ -2765,12 +2951,12 @@
         <v>37</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C41" s="1">
-        <v>502352</v>
-      </c>
-      <c r="D41" s="4" t="s">
+        <v>502350</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="1">
@@ -2798,15 +2984,15 @@
         <v>38</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C42" s="1">
-        <v>266596</v>
+        <v>502351</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="1">
+        <v>10</v>
+      </c>
+      <c r="E42" s="7">
         <v>0</v>
       </c>
       <c r="F42" s="1"/>
@@ -2831,15 +3017,15 @@
         <v>39</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" s="1">
-        <v>266597</v>
+        <v>502352</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E43" s="1">
+        <v>10</v>
+      </c>
+      <c r="E43" s="7">
         <v>0</v>
       </c>
       <c r="F43" s="1"/>
@@ -2867,12 +3053,12 @@
         <v>48</v>
       </c>
       <c r="C44" s="1">
-        <v>266598</v>
+        <v>266596</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="7">
         <v>0</v>
       </c>
       <c r="F44" s="1"/>
@@ -2900,12 +3086,12 @@
         <v>48</v>
       </c>
       <c r="C45" s="1">
-        <v>266600</v>
+        <v>266597</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="7">
         <v>0</v>
       </c>
       <c r="F45" s="1"/>
@@ -2933,12 +3119,12 @@
         <v>48</v>
       </c>
       <c r="C46" s="1">
-        <v>266601</v>
+        <v>266598</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="7">
         <v>0</v>
       </c>
       <c r="F46" s="1"/>
@@ -2966,12 +3152,12 @@
         <v>48</v>
       </c>
       <c r="C47" s="1">
-        <v>266602</v>
+        <v>266600</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="7">
         <v>0</v>
       </c>
       <c r="F47" s="1"/>
@@ -2999,12 +3185,12 @@
         <v>48</v>
       </c>
       <c r="C48" s="1">
-        <v>266610</v>
+        <v>266601</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="7">
         <v>0</v>
       </c>
       <c r="F48" s="1"/>
@@ -3029,13 +3215,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C49" s="1">
-        <v>467603</v>
+        <v>266602</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
@@ -3062,13 +3248,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C50" s="1">
-        <v>266332</v>
+        <v>266610</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
@@ -3095,13 +3281,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C51" s="1">
-        <v>457013</v>
+        <v>467603</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
@@ -3128,13 +3314,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C52" s="1">
-        <v>209534</v>
+        <v>266332</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
@@ -3161,13 +3347,13 @@
         <v>49</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C53" s="1">
-        <v>112801</v>
+        <v>457013</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
@@ -3194,13 +3380,13 @@
         <v>50</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C54" s="1">
-        <v>173867</v>
+        <v>209534</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
@@ -3226,14 +3412,14 @@
       <c r="A55" s="1">
         <v>51</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>62</v>
+      <c r="B55" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C55" s="1">
-        <v>26146</v>
+        <v>112801</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
@@ -3259,14 +3445,14 @@
       <c r="A56" s="1">
         <v>52</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>64</v>
+      <c r="B56" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C56" s="1">
-        <v>26151</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>10</v>
+        <v>173867</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -3292,9 +3478,11 @@
       <c r="A57" s="1">
         <v>53</v>
       </c>
-      <c r="B57" s="1"/>
+      <c r="B57" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="C57" s="1">
-        <v>26155</v>
+        <v>26146</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>63</v>
@@ -3324,13 +3512,13 @@
         <v>54</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C58" s="1">
-        <v>160743</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>63</v>
+        <v>26151</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
@@ -3356,14 +3544,12 @@
       <c r="A59" s="1">
         <v>55</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="B59" s="1"/>
       <c r="C59" s="1">
-        <v>162012</v>
+        <v>26155</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
@@ -3390,13 +3576,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C60" s="1">
-        <v>168959</v>
+        <v>160743</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
@@ -3423,13 +3609,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C61" s="1">
-        <v>200925</v>
+        <v>162012</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
@@ -3456,13 +3642,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C62" s="1">
-        <v>403000</v>
+        <v>168959</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
@@ -3489,13 +3675,13 @@
         <v>59</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C63" s="1">
-        <v>403004</v>
+        <v>200925</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
@@ -3525,7 +3711,7 @@
         <v>69</v>
       </c>
       <c r="C64" s="1">
-        <v>403012</v>
+        <v>403000</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>10</v>
@@ -3558,7 +3744,7 @@
         <v>69</v>
       </c>
       <c r="C65" s="1">
-        <v>403014</v>
+        <v>403004</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>10</v>
@@ -3591,7 +3777,7 @@
         <v>69</v>
       </c>
       <c r="C66" s="1">
-        <v>403015</v>
+        <v>403012</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>10</v>
@@ -3621,15 +3807,15 @@
         <v>63</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C67" s="1">
-        <v>506842</v>
+        <v>403014</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="7">
         <v>0</v>
       </c>
       <c r="F67" s="1"/>
@@ -3650,11 +3836,21 @@
       <c r="U67" s="1"/>
     </row>
     <row r="68" spans="1:21">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
+      <c r="A68" s="1">
+        <v>64</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" s="1">
+        <v>403015</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0</v>
+      </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -3673,11 +3869,21 @@
       <c r="U68" s="1"/>
     </row>
     <row r="69" spans="1:21">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
+      <c r="A69" s="1">
+        <v>65</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" s="1">
+        <v>506842</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="7">
+        <v>0</v>
+      </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -3696,11 +3902,21 @@
       <c r="U69" s="1"/>
     </row>
     <row r="70" spans="1:21">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
+      <c r="A70" s="1">
+        <v>66</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="1">
+        <v>442771</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E70" s="7">
+        <v>0</v>
+      </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -3719,11 +3935,21 @@
       <c r="U70" s="1"/>
     </row>
     <row r="71" spans="1:21">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
+      <c r="A71" s="1">
+        <v>67</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="1">
+        <v>234390</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0</v>
+      </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -3742,11 +3968,19 @@
       <c r="U71" s="1"/>
     </row>
     <row r="72" spans="1:21">
-      <c r="A72" s="1"/>
+      <c r="A72" s="1">
+        <v>68</v>
+      </c>
       <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
+      <c r="C72" s="1">
+        <v>292089</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="7">
+        <v>0</v>
+      </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -3764,12 +3998,20 @@
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
     </row>
-    <row r="73" spans="1:21">
-      <c r="A73" s="1"/>
+    <row r="73" ht="17.25" spans="1:21">
+      <c r="A73" s="1">
+        <v>69</v>
+      </c>
       <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
+      <c r="C73" s="5">
+        <v>72681</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="7">
+        <v>0</v>
+      </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -3787,12 +4029,20 @@
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
     </row>
-    <row r="74" spans="1:21">
-      <c r="A74" s="1"/>
+    <row r="74" ht="17.25" spans="1:21">
+      <c r="A74" s="1">
+        <v>70</v>
+      </c>
       <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
+      <c r="C74" s="5">
+        <v>72689</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -3810,12 +4060,20 @@
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
     </row>
-    <row r="75" spans="1:21">
-      <c r="A75" s="1"/>
+    <row r="75" ht="17.25" spans="1:21">
+      <c r="A75" s="1">
+        <v>71</v>
+      </c>
       <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
+      <c r="C75" s="5">
+        <v>44268</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -3833,12 +4091,20 @@
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
     </row>
-    <row r="76" spans="1:21">
-      <c r="A76" s="1"/>
+    <row r="76" ht="17.25" spans="1:21">
+      <c r="A76" s="1">
+        <v>72</v>
+      </c>
       <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
+      <c r="C76" s="5">
+        <v>72675</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -3856,12 +4122,20 @@
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
     </row>
-    <row r="77" spans="1:21">
-      <c r="A77" s="1"/>
+    <row r="77" ht="17.25" spans="1:21">
+      <c r="A77" s="1">
+        <v>73</v>
+      </c>
       <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
+      <c r="C77" s="5">
+        <v>68413</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
@@ -3879,12 +4153,20 @@
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
     </row>
-    <row r="78" spans="1:21">
-      <c r="A78" s="1"/>
+    <row r="78" ht="17.25" spans="1:21">
+      <c r="A78" s="1">
+        <v>74</v>
+      </c>
       <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
+      <c r="C78" s="5">
+        <v>266331</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -3902,12 +4184,20 @@
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
     </row>
-    <row r="79" spans="1:21">
-      <c r="A79" s="1"/>
+    <row r="79" ht="17.25" spans="1:21">
+      <c r="A79" s="1">
+        <v>75</v>
+      </c>
       <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
+      <c r="C79" s="5">
+        <v>386337</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -3925,12 +4215,20 @@
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
     </row>
-    <row r="80" spans="1:21">
-      <c r="A80" s="1"/>
+    <row r="80" ht="17.25" spans="1:21">
+      <c r="A80" s="1">
+        <v>76</v>
+      </c>
       <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
+      <c r="C80" s="5">
+        <v>173237</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -3948,12 +4246,20 @@
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
     </row>
-    <row r="81" spans="1:21">
-      <c r="A81" s="1"/>
+    <row r="81" ht="17.25" spans="1:21">
+      <c r="A81" s="1">
+        <v>77</v>
+      </c>
       <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
+      <c r="C81" s="5">
+        <v>173239</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -3971,12 +4277,20 @@
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
     </row>
-    <row r="82" spans="1:21">
-      <c r="A82" s="1"/>
+    <row r="82" ht="17.25" spans="1:21">
+      <c r="A82" s="1">
+        <v>78</v>
+      </c>
       <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
+      <c r="C82" s="5">
+        <v>173240</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -3994,12 +4308,20 @@
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
     </row>
-    <row r="83" spans="1:21">
-      <c r="A83" s="1"/>
+    <row r="83" ht="17.25" spans="1:21">
+      <c r="A83" s="1">
+        <v>79</v>
+      </c>
       <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
+      <c r="C83" s="5">
+        <v>173242</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E83" s="1">
+        <v>0</v>
+      </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -4017,12 +4339,20 @@
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
     </row>
-    <row r="84" spans="1:21">
-      <c r="A84" s="1"/>
+    <row r="84" ht="17.25" spans="1:21">
+      <c r="A84" s="1">
+        <v>80</v>
+      </c>
       <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
+      <c r="C84" s="5">
+        <v>173241</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -4040,12 +4370,20 @@
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
     </row>
-    <row r="85" spans="1:21">
-      <c r="A85" s="1"/>
+    <row r="85" ht="17.25" spans="1:21">
+      <c r="A85" s="1">
+        <v>81</v>
+      </c>
       <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
+      <c r="C85" s="5">
+        <v>173243</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -4063,12 +4401,20 @@
       <c r="T85" s="1"/>
       <c r="U85" s="1"/>
     </row>
-    <row r="86" spans="1:21">
-      <c r="A86" s="1"/>
+    <row r="86" ht="17.25" spans="1:21">
+      <c r="A86" s="1">
+        <v>82</v>
+      </c>
       <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
+      <c r="C86" s="5">
+        <v>173244</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E86" s="1">
+        <v>0</v>
+      </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -4086,12 +4432,20 @@
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
     </row>
-    <row r="87" spans="1:21">
-      <c r="A87" s="1"/>
+    <row r="87" ht="17.25" spans="1:21">
+      <c r="A87" s="1">
+        <v>83</v>
+      </c>
       <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
+      <c r="C87" s="5">
+        <v>173245</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E87" s="1">
+        <v>0</v>
+      </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -4109,12 +4463,20 @@
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
     </row>
-    <row r="88" spans="1:21">
-      <c r="A88" s="1"/>
+    <row r="88" ht="17.25" spans="1:21">
+      <c r="A88" s="1">
+        <v>84</v>
+      </c>
       <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
+      <c r="C88" s="5">
+        <v>173501</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E88" s="1">
+        <v>0</v>
+      </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -4132,12 +4494,20 @@
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
     </row>
-    <row r="89" spans="1:21">
-      <c r="A89" s="1"/>
+    <row r="89" ht="17.25" spans="1:21">
+      <c r="A89" s="1">
+        <v>85</v>
+      </c>
       <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
+      <c r="C89" s="5">
+        <v>173502</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E89" s="1">
+        <v>0</v>
+      </c>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -4155,12 +4525,20 @@
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
     </row>
-    <row r="90" spans="1:21">
-      <c r="A90" s="1"/>
+    <row r="90" ht="17.25" spans="1:21">
+      <c r="A90" s="1">
+        <v>86</v>
+      </c>
       <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
+      <c r="C90" s="5">
+        <v>173499</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -4178,12 +4556,20 @@
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
     </row>
-    <row r="91" spans="1:21">
-      <c r="A91" s="1"/>
+    <row r="91" ht="17.25" spans="1:21">
+      <c r="A91" s="1">
+        <v>87</v>
+      </c>
       <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
+      <c r="C91" s="5">
+        <v>173503</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -4201,12 +4587,20 @@
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
     </row>
-    <row r="92" spans="1:21">
-      <c r="A92" s="1"/>
+    <row r="92" ht="17.25" spans="1:21">
+      <c r="A92" s="1">
+        <v>88</v>
+      </c>
       <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
+      <c r="C92" s="5">
+        <v>173504</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E92" s="7">
+        <v>0</v>
+      </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -4224,12 +4618,20 @@
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
     </row>
-    <row r="93" spans="1:21">
-      <c r="A93" s="1"/>
+    <row r="93" ht="17.25" spans="1:21">
+      <c r="A93" s="1">
+        <v>89</v>
+      </c>
       <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
+      <c r="C93" s="5">
+        <v>173505</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E93" s="7">
+        <v>0</v>
+      </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -4247,12 +4649,20 @@
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
     </row>
-    <row r="94" spans="1:21">
-      <c r="A94" s="1"/>
+    <row r="94" ht="17.25" spans="1:21">
+      <c r="A94" s="1">
+        <v>90</v>
+      </c>
       <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
+      <c r="C94" s="5">
+        <v>173506</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E94" s="7">
+        <v>0</v>
+      </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
@@ -4270,12 +4680,20 @@
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
     </row>
-    <row r="95" spans="1:21">
-      <c r="A95" s="1"/>
+    <row r="95" ht="17.25" spans="1:21">
+      <c r="A95" s="1">
+        <v>91</v>
+      </c>
       <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
+      <c r="C95" s="5">
+        <v>173858</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E95" s="7">
+        <v>0</v>
+      </c>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
@@ -4293,12 +4711,20 @@
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
     </row>
-    <row r="96" spans="1:21">
-      <c r="A96" s="1"/>
+    <row r="96" ht="17.25" spans="1:21">
+      <c r="A96" s="1">
+        <v>92</v>
+      </c>
       <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
+      <c r="C96" s="5">
+        <v>173859</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E96" s="7">
+        <v>0</v>
+      </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
@@ -4316,12 +4742,20 @@
       <c r="T96" s="1"/>
       <c r="U96" s="1"/>
     </row>
-    <row r="97" spans="1:21">
-      <c r="A97" s="1"/>
+    <row r="97" ht="17.25" spans="1:21">
+      <c r="A97" s="1">
+        <v>93</v>
+      </c>
       <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
+      <c r="C97" s="5">
+        <v>173860</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E97" s="7">
+        <v>0</v>
+      </c>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
@@ -4339,12 +4773,20 @@
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
     </row>
-    <row r="98" spans="1:21">
-      <c r="A98" s="1"/>
+    <row r="98" ht="17.25" spans="1:21">
+      <c r="A98" s="1">
+        <v>94</v>
+      </c>
       <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
+      <c r="C98" s="5">
+        <v>173861</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E98" s="7">
+        <v>0</v>
+      </c>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
@@ -4362,12 +4804,20 @@
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
     </row>
-    <row r="99" spans="1:21">
-      <c r="A99" s="1"/>
+    <row r="99" ht="17.25" spans="1:21">
+      <c r="A99" s="1">
+        <v>95</v>
+      </c>
       <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
+      <c r="C99" s="5">
+        <v>173862</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -4385,12 +4835,20 @@
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
     </row>
-    <row r="100" spans="1:21">
-      <c r="A100" s="1"/>
+    <row r="100" ht="17.25" spans="1:21">
+      <c r="A100" s="1">
+        <v>96</v>
+      </c>
       <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
+      <c r="C100" s="5">
+        <v>173863</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
@@ -4408,12 +4866,20 @@
       <c r="T100" s="1"/>
       <c r="U100" s="1"/>
     </row>
-    <row r="101" spans="1:21">
-      <c r="A101" s="1"/>
+    <row r="101" ht="17.25" spans="1:21">
+      <c r="A101" s="1">
+        <v>97</v>
+      </c>
       <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
+      <c r="C101" s="5">
+        <v>173864</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
@@ -4431,12 +4897,20 @@
       <c r="T101" s="1"/>
       <c r="U101" s="1"/>
     </row>
-    <row r="102" spans="1:21">
-      <c r="A102" s="1"/>
+    <row r="102" ht="17.25" spans="1:21">
+      <c r="A102" s="1">
+        <v>98</v>
+      </c>
       <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
+      <c r="C102" s="5">
+        <v>173865</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E102" s="1">
+        <v>0</v>
+      </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
@@ -4454,12 +4928,20 @@
       <c r="T102" s="1"/>
       <c r="U102" s="1"/>
     </row>
-    <row r="103" spans="1:21">
-      <c r="A103" s="1"/>
+    <row r="103" ht="17.25" spans="1:21">
+      <c r="A103" s="1">
+        <v>99</v>
+      </c>
       <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
+      <c r="C103" s="5">
+        <v>173866</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E103" s="1">
+        <v>0</v>
+      </c>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
@@ -4477,12 +4959,20 @@
       <c r="T103" s="1"/>
       <c r="U103" s="1"/>
     </row>
-    <row r="104" spans="1:21">
-      <c r="A104" s="1"/>
+    <row r="104" ht="17.25" spans="1:21">
+      <c r="A104" s="1">
+        <v>100</v>
+      </c>
       <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
+      <c r="C104" s="5">
+        <v>390761</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E104" s="1">
+        <v>0</v>
+      </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
@@ -4500,12 +4990,20 @@
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
     </row>
-    <row r="105" spans="1:21">
-      <c r="A105" s="1"/>
+    <row r="105" ht="17.25" spans="1:21">
+      <c r="A105" s="1">
+        <v>101</v>
+      </c>
       <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
+      <c r="C105" s="5">
+        <v>314053</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E105" s="1">
+        <v>0</v>
+      </c>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
@@ -4523,12 +5021,20 @@
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
     </row>
-    <row r="106" spans="1:21">
-      <c r="A106" s="1"/>
+    <row r="106" ht="17.25" spans="1:21">
+      <c r="A106" s="1">
+        <v>102</v>
+      </c>
       <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
+      <c r="C106" s="5">
+        <v>68397</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E106" s="1">
+        <v>0</v>
+      </c>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
       <c r="H106" s="1"/>
@@ -4546,12 +5052,20 @@
       <c r="T106" s="1"/>
       <c r="U106" s="1"/>
     </row>
-    <row r="107" spans="1:21">
-      <c r="A107" s="1"/>
+    <row r="107" ht="17.25" spans="1:21">
+      <c r="A107" s="1">
+        <v>103</v>
+      </c>
       <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
+      <c r="C107" s="5">
+        <v>504881</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E107" s="1">
+        <v>0</v>
+      </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
@@ -4569,12 +5083,20 @@
       <c r="T107" s="1"/>
       <c r="U107" s="1"/>
     </row>
-    <row r="108" spans="1:21">
-      <c r="A108" s="1"/>
+    <row r="108" ht="17.25" spans="1:21">
+      <c r="A108" s="1">
+        <v>104</v>
+      </c>
       <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
+      <c r="C108" s="5">
+        <v>68430</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E108" s="1">
+        <v>0</v>
+      </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
@@ -4592,12 +5114,20 @@
       <c r="T108" s="1"/>
       <c r="U108" s="1"/>
     </row>
-    <row r="109" spans="1:21">
-      <c r="A109" s="1"/>
+    <row r="109" ht="17.25" spans="1:21">
+      <c r="A109" s="1">
+        <v>105</v>
+      </c>
       <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
+      <c r="C109" s="5">
+        <v>68462</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E109" s="1">
+        <v>0</v>
+      </c>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
@@ -4615,12 +5145,20 @@
       <c r="T109" s="1"/>
       <c r="U109" s="1"/>
     </row>
-    <row r="110" spans="1:21">
-      <c r="A110" s="1"/>
+    <row r="110" ht="17.25" spans="1:21">
+      <c r="A110" s="1">
+        <v>106</v>
+      </c>
       <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
+      <c r="C110" s="5">
+        <v>68404</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E110" s="1">
+        <v>0</v>
+      </c>
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
@@ -4638,12 +5176,20 @@
       <c r="T110" s="1"/>
       <c r="U110" s="1"/>
     </row>
-    <row r="111" spans="1:21">
-      <c r="A111" s="1"/>
+    <row r="111" ht="17.25" spans="1:21">
+      <c r="A111" s="1">
+        <v>107</v>
+      </c>
       <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
+      <c r="C111" s="5">
+        <v>68406</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E111" s="1">
+        <v>0</v>
+      </c>
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
@@ -4661,12 +5207,20 @@
       <c r="T111" s="1"/>
       <c r="U111" s="1"/>
     </row>
-    <row r="112" spans="1:21">
-      <c r="A112" s="1"/>
+    <row r="112" ht="17.25" spans="1:21">
+      <c r="A112" s="1">
+        <v>108</v>
+      </c>
       <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
+      <c r="C112" s="5">
+        <v>68410</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E112" s="1">
+        <v>0</v>
+      </c>
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
@@ -4684,12 +5238,20 @@
       <c r="T112" s="1"/>
       <c r="U112" s="1"/>
     </row>
-    <row r="113" spans="1:21">
-      <c r="A113" s="1"/>
+    <row r="113" ht="17.25" spans="1:21">
+      <c r="A113" s="1">
+        <v>109</v>
+      </c>
       <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
+      <c r="C113" s="5">
+        <v>68422</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E113" s="1">
+        <v>0</v>
+      </c>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
@@ -4707,12 +5269,20 @@
       <c r="T113" s="1"/>
       <c r="U113" s="1"/>
     </row>
-    <row r="114" spans="1:21">
-      <c r="A114" s="1"/>
+    <row r="114" ht="17.25" spans="1:21">
+      <c r="A114" s="1">
+        <v>110</v>
+      </c>
       <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
+      <c r="C114" s="5">
+        <v>68424</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E114" s="1">
+        <v>0</v>
+      </c>
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
       <c r="H114" s="1"/>
@@ -4730,12 +5300,20 @@
       <c r="T114" s="1"/>
       <c r="U114" s="1"/>
     </row>
-    <row r="115" spans="1:21">
-      <c r="A115" s="1"/>
+    <row r="115" ht="17.25" spans="1:21">
+      <c r="A115" s="1">
+        <v>111</v>
+      </c>
       <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
+      <c r="C115" s="5">
+        <v>68427</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E115" s="1">
+        <v>0</v>
+      </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
@@ -4753,12 +5331,20 @@
       <c r="T115" s="1"/>
       <c r="U115" s="1"/>
     </row>
-    <row r="116" spans="1:21">
-      <c r="A116" s="1"/>
+    <row r="116" ht="17.25" spans="1:21">
+      <c r="A116" s="1">
+        <v>112</v>
+      </c>
       <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
+      <c r="C116" s="5">
+        <v>68432</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E116" s="1">
+        <v>0</v>
+      </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
@@ -4776,12 +5362,20 @@
       <c r="T116" s="1"/>
       <c r="U116" s="1"/>
     </row>
-    <row r="117" spans="1:21">
-      <c r="A117" s="1"/>
+    <row r="117" ht="17.25" spans="1:21">
+      <c r="A117" s="1">
+        <v>113</v>
+      </c>
       <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
+      <c r="C117" s="5">
+        <v>68434</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E117" s="7">
+        <v>0</v>
+      </c>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
@@ -4799,12 +5393,20 @@
       <c r="T117" s="1"/>
       <c r="U117" s="1"/>
     </row>
-    <row r="118" spans="1:21">
-      <c r="A118" s="1"/>
+    <row r="118" ht="17.25" spans="1:21">
+      <c r="A118" s="1">
+        <v>114</v>
+      </c>
       <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
+      <c r="C118" s="5">
+        <v>68436</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E118" s="7">
+        <v>0</v>
+      </c>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
@@ -4822,12 +5424,20 @@
       <c r="T118" s="1"/>
       <c r="U118" s="1"/>
     </row>
-    <row r="119" spans="1:21">
-      <c r="A119" s="1"/>
+    <row r="119" ht="17.25" spans="1:21">
+      <c r="A119" s="1">
+        <v>115</v>
+      </c>
       <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-      <c r="E119" s="1"/>
+      <c r="C119" s="5">
+        <v>68438</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E119" s="7">
+        <v>0</v>
+      </c>
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
@@ -4845,12 +5455,20 @@
       <c r="T119" s="1"/>
       <c r="U119" s="1"/>
     </row>
-    <row r="120" spans="1:21">
-      <c r="A120" s="1"/>
+    <row r="120" ht="17.25" spans="1:21">
+      <c r="A120" s="1">
+        <v>116</v>
+      </c>
       <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="1"/>
+      <c r="C120" s="5">
+        <v>68440</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E120" s="7">
+        <v>0</v>
+      </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
@@ -4868,12 +5486,20 @@
       <c r="T120" s="1"/>
       <c r="U120" s="1"/>
     </row>
-    <row r="121" spans="1:21">
-      <c r="A121" s="1"/>
+    <row r="121" ht="17.25" spans="1:21">
+      <c r="A121" s="1">
+        <v>117</v>
+      </c>
       <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
+      <c r="C121" s="5">
+        <v>68442</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E121" s="7">
+        <v>0</v>
+      </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -4891,12 +5517,20 @@
       <c r="T121" s="1"/>
       <c r="U121" s="1"/>
     </row>
-    <row r="122" spans="1:21">
-      <c r="A122" s="1"/>
+    <row r="122" ht="17.25" spans="1:21">
+      <c r="A122" s="1">
+        <v>118</v>
+      </c>
       <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
+      <c r="C122" s="5">
+        <v>68447</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E122" s="7">
+        <v>0</v>
+      </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -4914,12 +5548,20 @@
       <c r="T122" s="1"/>
       <c r="U122" s="1"/>
     </row>
-    <row r="123" spans="1:21">
-      <c r="A123" s="1"/>
+    <row r="123" ht="17.25" spans="1:21">
+      <c r="A123" s="1">
+        <v>119</v>
+      </c>
       <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
+      <c r="C123" s="5">
+        <v>68449</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E123" s="7">
+        <v>0</v>
+      </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
@@ -4937,12 +5579,20 @@
       <c r="T123" s="1"/>
       <c r="U123" s="1"/>
     </row>
-    <row r="124" spans="1:21">
-      <c r="A124" s="1"/>
+    <row r="124" ht="17.25" spans="1:21">
+      <c r="A124" s="1">
+        <v>120</v>
+      </c>
       <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
+      <c r="C124" s="5">
+        <v>68452</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E124" s="1">
+        <v>0</v>
+      </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
@@ -4960,12 +5610,20 @@
       <c r="T124" s="1"/>
       <c r="U124" s="1"/>
     </row>
-    <row r="125" spans="1:21">
-      <c r="A125" s="1"/>
+    <row r="125" ht="17.25" spans="1:21">
+      <c r="A125" s="1">
+        <v>121</v>
+      </c>
       <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
+      <c r="C125" s="5">
+        <v>68456</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E125" s="1">
+        <v>0</v>
+      </c>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
@@ -4983,12 +5641,20 @@
       <c r="T125" s="1"/>
       <c r="U125" s="1"/>
     </row>
-    <row r="126" spans="1:21">
-      <c r="A126" s="1"/>
+    <row r="126" ht="17.25" spans="1:21">
+      <c r="A126" s="1">
+        <v>122</v>
+      </c>
       <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
+      <c r="C126" s="5">
+        <v>111667</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E126" s="1">
+        <v>0</v>
+      </c>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
@@ -5006,12 +5672,20 @@
       <c r="T126" s="1"/>
       <c r="U126" s="1"/>
     </row>
-    <row r="127" spans="1:21">
-      <c r="A127" s="1"/>
+    <row r="127" ht="17.25" spans="1:21">
+      <c r="A127" s="1">
+        <v>123</v>
+      </c>
       <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
+      <c r="C127" s="5">
+        <v>111668</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E127" s="1">
+        <v>0</v>
+      </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -5029,12 +5703,20 @@
       <c r="T127" s="1"/>
       <c r="U127" s="1"/>
     </row>
-    <row r="128" spans="1:21">
-      <c r="A128" s="1"/>
+    <row r="128" ht="17.25" spans="1:21">
+      <c r="A128" s="1">
+        <v>124</v>
+      </c>
       <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-      <c r="E128" s="1"/>
+      <c r="C128" s="5">
+        <v>111669</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E128" s="1">
+        <v>0</v>
+      </c>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
@@ -5052,12 +5734,20 @@
       <c r="T128" s="1"/>
       <c r="U128" s="1"/>
     </row>
-    <row r="129" spans="1:21">
-      <c r="A129" s="1"/>
+    <row r="129" ht="17.25" spans="1:21">
+      <c r="A129" s="1">
+        <v>125</v>
+      </c>
       <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1"/>
+      <c r="C129" s="5">
+        <v>117848</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E129" s="1">
+        <v>0</v>
+      </c>
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
@@ -5075,12 +5765,20 @@
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
     </row>
-    <row r="130" spans="1:21">
-      <c r="A130" s="1"/>
+    <row r="130" ht="17.25" spans="1:21">
+      <c r="A130" s="1">
+        <v>126</v>
+      </c>
       <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-      <c r="E130" s="1"/>
+      <c r="C130" s="5">
+        <v>134224</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E130" s="1">
+        <v>0</v>
+      </c>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
@@ -5098,12 +5796,20 @@
       <c r="T130" s="1"/>
       <c r="U130" s="1"/>
     </row>
-    <row r="131" spans="1:21">
-      <c r="A131" s="1"/>
+    <row r="131" ht="17.25" spans="1:21">
+      <c r="A131" s="1">
+        <v>127</v>
+      </c>
       <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
+      <c r="C131" s="5">
+        <v>174438</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E131" s="1">
+        <v>0</v>
+      </c>
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
@@ -5121,12 +5827,20 @@
       <c r="T131" s="1"/>
       <c r="U131" s="1"/>
     </row>
-    <row r="132" spans="1:21">
-      <c r="A132" s="1"/>
+    <row r="132" ht="17.25" spans="1:21">
+      <c r="A132" s="1">
+        <v>128</v>
+      </c>
       <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="1"/>
+      <c r="C132" s="5">
+        <v>182167</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E132" s="1">
+        <v>0</v>
+      </c>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
       <c r="H132" s="1"/>
@@ -5144,12 +5858,20 @@
       <c r="T132" s="1"/>
       <c r="U132" s="1"/>
     </row>
-    <row r="133" spans="1:21">
-      <c r="A133" s="1"/>
+    <row r="133" ht="17.25" spans="1:21">
+      <c r="A133" s="1">
+        <v>129</v>
+      </c>
       <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
+      <c r="C133" s="5">
+        <v>186725</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E133" s="1">
+        <v>0</v>
+      </c>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
@@ -5167,12 +5889,20 @@
       <c r="T133" s="1"/>
       <c r="U133" s="1"/>
     </row>
-    <row r="134" spans="1:21">
-      <c r="A134" s="1"/>
+    <row r="134" ht="17.25" spans="1:21">
+      <c r="A134" s="1">
+        <v>130</v>
+      </c>
       <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
-      <c r="E134" s="1"/>
+      <c r="C134" s="5">
+        <v>186901</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E134" s="1">
+        <v>0</v>
+      </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
@@ -5190,12 +5920,20 @@
       <c r="T134" s="1"/>
       <c r="U134" s="1"/>
     </row>
-    <row r="135" spans="1:21">
-      <c r="A135" s="1"/>
+    <row r="135" ht="17.25" spans="1:21">
+      <c r="A135" s="1">
+        <v>131</v>
+      </c>
       <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
-      <c r="E135" s="1"/>
+      <c r="C135" s="5">
+        <v>191858</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E135" s="1">
+        <v>0</v>
+      </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
@@ -5213,12 +5951,20 @@
       <c r="T135" s="1"/>
       <c r="U135" s="1"/>
     </row>
-    <row r="136" spans="1:21">
-      <c r="A136" s="1"/>
+    <row r="136" ht="17.25" spans="1:21">
+      <c r="A136" s="1">
+        <v>132</v>
+      </c>
       <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
-      <c r="E136" s="1"/>
+      <c r="C136" s="5">
+        <v>192738</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E136" s="1">
+        <v>0</v>
+      </c>
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
@@ -5236,12 +5982,20 @@
       <c r="T136" s="1"/>
       <c r="U136" s="1"/>
     </row>
-    <row r="137" spans="1:21">
-      <c r="A137" s="1"/>
+    <row r="137" ht="17.25" spans="1:21">
+      <c r="A137" s="1">
+        <v>133</v>
+      </c>
       <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-      <c r="E137" s="1"/>
+      <c r="C137" s="5">
+        <v>192739</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E137" s="1">
+        <v>0</v>
+      </c>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
@@ -5259,12 +6013,20 @@
       <c r="T137" s="1"/>
       <c r="U137" s="1"/>
     </row>
-    <row r="138" spans="1:21">
-      <c r="A138" s="1"/>
+    <row r="138" ht="17.25" spans="1:21">
+      <c r="A138" s="1">
+        <v>134</v>
+      </c>
       <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
-      <c r="E138" s="1"/>
+      <c r="C138" s="5">
+        <v>192740</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E138" s="1">
+        <v>0</v>
+      </c>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
@@ -5282,12 +6044,20 @@
       <c r="T138" s="1"/>
       <c r="U138" s="1"/>
     </row>
-    <row r="139" spans="1:21">
-      <c r="A139" s="1"/>
+    <row r="139" ht="17.25" spans="1:21">
+      <c r="A139" s="1">
+        <v>135</v>
+      </c>
       <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
-      <c r="E139" s="1"/>
+      <c r="C139" s="5">
+        <v>192741</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E139" s="1">
+        <v>0</v>
+      </c>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
@@ -5305,12 +6075,20 @@
       <c r="T139" s="1"/>
       <c r="U139" s="1"/>
     </row>
-    <row r="140" spans="1:21">
-      <c r="A140" s="1"/>
+    <row r="140" ht="17.25" spans="1:21">
+      <c r="A140" s="1">
+        <v>136</v>
+      </c>
       <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
-      <c r="E140" s="1"/>
+      <c r="C140" s="5">
+        <v>202880</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E140" s="1">
+        <v>0</v>
+      </c>
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
@@ -5328,12 +6106,20 @@
       <c r="T140" s="1"/>
       <c r="U140" s="1"/>
     </row>
-    <row r="141" spans="1:21">
-      <c r="A141" s="1"/>
+    <row r="141" ht="17.25" spans="1:21">
+      <c r="A141" s="1">
+        <v>137</v>
+      </c>
       <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
-      <c r="E141" s="1"/>
+      <c r="C141" s="5">
+        <v>266537</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E141" s="1">
+        <v>0</v>
+      </c>
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
@@ -5351,12 +6137,20 @@
       <c r="T141" s="1"/>
       <c r="U141" s="1"/>
     </row>
-    <row r="142" spans="1:21">
-      <c r="A142" s="1"/>
+    <row r="142" ht="17.25" spans="1:21">
+      <c r="A142" s="1">
+        <v>138</v>
+      </c>
       <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
-      <c r="E142" s="1"/>
+      <c r="C142" s="5">
+        <v>286443</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E142" s="7">
+        <v>0</v>
+      </c>
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
@@ -5374,12 +6168,20 @@
       <c r="T142" s="1"/>
       <c r="U142" s="1"/>
     </row>
-    <row r="143" spans="1:21">
-      <c r="A143" s="1"/>
+    <row r="143" ht="17.25" spans="1:21">
+      <c r="A143" s="1">
+        <v>139</v>
+      </c>
       <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
-      <c r="E143" s="1"/>
+      <c r="C143" s="5">
+        <v>323565</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E143" s="7">
+        <v>0</v>
+      </c>
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -5397,12 +6199,20 @@
       <c r="T143" s="1"/>
       <c r="U143" s="1"/>
     </row>
-    <row r="144" spans="1:21">
-      <c r="A144" s="1"/>
+    <row r="144" ht="17.25" spans="1:21">
+      <c r="A144" s="1">
+        <v>140</v>
+      </c>
       <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
-      <c r="E144" s="1"/>
+      <c r="C144" s="5">
+        <v>351369</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E144" s="7">
+        <v>0</v>
+      </c>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
@@ -5420,12 +6230,20 @@
       <c r="T144" s="1"/>
       <c r="U144" s="1"/>
     </row>
-    <row r="145" spans="1:21">
-      <c r="A145" s="1"/>
+    <row r="145" ht="17.25" spans="1:21">
+      <c r="A145" s="1">
+        <v>141</v>
+      </c>
       <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
-      <c r="E145" s="1"/>
+      <c r="C145" s="5">
+        <v>363651</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E145" s="7">
+        <v>0</v>
+      </c>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -5443,12 +6261,20 @@
       <c r="T145" s="1"/>
       <c r="U145" s="1"/>
     </row>
-    <row r="146" spans="1:21">
-      <c r="A146" s="1"/>
+    <row r="146" ht="17.25" spans="1:21">
+      <c r="A146" s="1">
+        <v>142</v>
+      </c>
       <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
-      <c r="E146" s="1"/>
+      <c r="C146" s="5">
+        <v>374517</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E146" s="7">
+        <v>0</v>
+      </c>
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
@@ -5466,12 +6292,20 @@
       <c r="T146" s="1"/>
       <c r="U146" s="1"/>
     </row>
-    <row r="147" spans="1:21">
-      <c r="A147" s="1"/>
+    <row r="147" ht="17.25" spans="1:21">
+      <c r="A147" s="1">
+        <v>143</v>
+      </c>
       <c r="B147" s="1"/>
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
-      <c r="E147" s="1"/>
+      <c r="C147" s="5">
+        <v>384900</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E147" s="7">
+        <v>0</v>
+      </c>
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
@@ -5489,12 +6323,20 @@
       <c r="T147" s="1"/>
       <c r="U147" s="1"/>
     </row>
-    <row r="148" spans="1:21">
-      <c r="A148" s="1"/>
+    <row r="148" ht="17.25" spans="1:21">
+      <c r="A148" s="1">
+        <v>144</v>
+      </c>
       <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
-      <c r="E148" s="1"/>
+      <c r="C148" s="5">
+        <v>390760</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E148" s="7">
+        <v>0</v>
+      </c>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
@@ -5512,12 +6354,20 @@
       <c r="T148" s="1"/>
       <c r="U148" s="1"/>
     </row>
-    <row r="149" spans="1:21">
-      <c r="A149" s="1"/>
+    <row r="149" ht="17.25" spans="1:21">
+      <c r="A149" s="1">
+        <v>145</v>
+      </c>
       <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
-      <c r="E149" s="1"/>
+      <c r="C149" s="5">
+        <v>457460</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E149" s="1">
+        <v>0</v>
+      </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
@@ -5535,10 +6385,10 @@
       <c r="T149" s="1"/>
       <c r="U149" s="1"/>
     </row>
-    <row r="150" spans="1:21">
+    <row r="150" ht="17.25" spans="1:21">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
+      <c r="C150" s="5"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
